--- a/output/pdf_financials_xlsx/AUOZ.xlsx
+++ b/output/pdf_financials_xlsx/AUOZ.xlsx
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.603503</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.249756</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.094953</v>
       </c>
     </row>
     <row r="93">
@@ -3167,7 +3167,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="n">
         <v>0.603503</v>
       </c>

--- a/output/pdf_financials_xlsx/AUOZ.xlsx
+++ b/output/pdf_financials_xlsx/AUOZ.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.115568</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.118919</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.104498</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.063308</v>
+        <v>-1.178876</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.143567</v>
+        <v>-2.262486</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.755714</v>
+        <v>-2.860212</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.063308</v>
+        <v>-1.178876</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.143567</v>
+        <v>-2.262486</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.755714</v>
+        <v>-2.860212</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.775214</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.248308</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>8.817069999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.026075</v>
+        <v>1.801289</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.027186</v>
+        <v>0.275494</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>8.817069999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.244645</v>
+        <v>0.469431</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.52361</v>
+        <v>0.275302</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>9.223765999999999</v>
+        <v>0.406696</v>
       </c>
     </row>
     <row r="49">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">

--- a/output/pdf_financials_xlsx/AUOZ.xlsx
+++ b/output/pdf_financials_xlsx/AUOZ.xlsx
@@ -880,10 +880,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.036126</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.034181</v>
       </c>
     </row>
     <row r="29">
@@ -896,10 +896,10 @@
         <v>-1.178876</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.262486</v>
+        <v>-2.22636</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.860212</v>
+        <v>-2.826031</v>
       </c>
     </row>
     <row r="30">
@@ -2038,10 +2038,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.036126</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.034181</v>
       </c>
     </row>
     <row r="101">
@@ -4203,7 +4203,11 @@
           <t>Depreciation of right-of-use assets $</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AUOZ.xlsx
+++ b/output/pdf_financials_xlsx/AUOZ.xlsx
@@ -1510,13 +1510,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.163234</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.047854</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.220759</v>
       </c>
     </row>
     <row r="68">
@@ -4507,7 +4507,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
         <v>3.54934</v>
       </c>
